--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129737606</v>
       </c>
       <c r="B2" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129737623</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129737717</v>
       </c>
       <c r="B4" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129737855</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,52 +1099,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129737898</v>
+        <v>129737526</v>
       </c>
       <c r="B6" t="n">
-        <v>58105</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A56370, Mörghult, Sm</t>
+          <t>A 56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584009</v>
+        <v>584110</v>
       </c>
       <c r="R6" t="n">
-        <v>6401446</v>
+        <v>6401356</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,60 +1208,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129737526</v>
+        <v>129737898</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>58106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 56370, Mörghult, Sm</t>
+          <t>A56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584110</v>
+        <v>584009</v>
       </c>
       <c r="R7" t="n">
-        <v>6401356</v>
+        <v>6401446</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>129737728</v>
       </c>
       <c r="B8" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>129737570</v>
       </c>
       <c r="B9" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>129737757</v>
       </c>
       <c r="B10" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>129737706</v>
       </c>
       <c r="B11" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>129737591</v>
       </c>
       <c r="B12" t="n">
-        <v>91571</v>
+        <v>91572</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>129737556</v>
       </c>
       <c r="B13" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -1736,45 +1736,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129737591</v>
+        <v>129737556</v>
       </c>
       <c r="B12" t="n">
-        <v>91572</v>
+        <v>98769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1782,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583974</v>
+        <v>584067</v>
       </c>
       <c r="R12" t="n">
-        <v>6401513</v>
+        <v>6401372</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,11 +1819,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På högstubbe av asp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,46 +1846,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129737556</v>
+        <v>129737591</v>
       </c>
       <c r="B13" t="n">
-        <v>98769</v>
+        <v>91577</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1897,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584067</v>
+        <v>583974</v>
       </c>
       <c r="R13" t="n">
-        <v>6401372</v>
+        <v>6401513</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,6 +1928,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På högstubbe av asp</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129737606</v>
       </c>
       <c r="B2" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129737623</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129737717</v>
       </c>
       <c r="B4" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129737855</v>
       </c>
       <c r="B5" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,60 +1099,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129737526</v>
+        <v>129737898</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>58106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 56370, Mörghult, Sm</t>
+          <t>A56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584110</v>
+        <v>584009</v>
       </c>
       <c r="R6" t="n">
-        <v>6401356</v>
+        <v>6401446</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,52 +1200,60 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129737898</v>
+        <v>129737526</v>
       </c>
       <c r="B7" t="n">
-        <v>58106</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A56370, Mörghult, Sm</t>
+          <t>A 56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584009</v>
+        <v>584110</v>
       </c>
       <c r="R7" t="n">
-        <v>6401446</v>
+        <v>6401356</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>129737728</v>
       </c>
       <c r="B8" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>129737570</v>
       </c>
       <c r="B9" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>129737706</v>
       </c>
       <c r="B11" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>129737556</v>
       </c>
       <c r="B12" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -1099,52 +1099,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129737898</v>
+        <v>129737526</v>
       </c>
       <c r="B6" t="n">
-        <v>58106</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A56370, Mörghult, Sm</t>
+          <t>A 56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584009</v>
+        <v>584110</v>
       </c>
       <c r="R6" t="n">
-        <v>6401446</v>
+        <v>6401356</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,60 +1208,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129737526</v>
+        <v>129737898</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>58106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 56370, Mörghult, Sm</t>
+          <t>A56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584110</v>
+        <v>584009</v>
       </c>
       <c r="R7" t="n">
-        <v>6401356</v>
+        <v>6401446</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -1099,60 +1099,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129737526</v>
+        <v>129737898</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>58106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 56370, Mörghult, Sm</t>
+          <t>A56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584110</v>
+        <v>584009</v>
       </c>
       <c r="R6" t="n">
-        <v>6401356</v>
+        <v>6401446</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,52 +1200,60 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129737898</v>
+        <v>129737526</v>
       </c>
       <c r="B7" t="n">
-        <v>58106</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A56370, Mörghult, Sm</t>
+          <t>A 56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584009</v>
+        <v>584110</v>
       </c>
       <c r="R7" t="n">
-        <v>6401446</v>
+        <v>6401356</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129737606</v>
       </c>
       <c r="B2" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129737623</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129737717</v>
       </c>
       <c r="B4" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129737855</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>129737728</v>
       </c>
       <c r="B8" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>129737570</v>
       </c>
       <c r="B9" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>129737706</v>
       </c>
       <c r="B11" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>129737556</v>
       </c>
       <c r="B12" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>129737591</v>
       </c>
       <c r="B13" t="n">
-        <v>91577</v>
+        <v>91581</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129737606</v>
       </c>
       <c r="B2" t="n">
-        <v>105844</v>
+        <v>105846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129737623</v>
       </c>
       <c r="B3" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129737717</v>
       </c>
       <c r="B4" t="n">
-        <v>105844</v>
+        <v>105846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129737855</v>
       </c>
       <c r="B5" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,52 +1099,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129737898</v>
+        <v>129737526</v>
       </c>
       <c r="B6" t="n">
-        <v>58106</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A56370, Mörghult, Sm</t>
+          <t>A 56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584009</v>
+        <v>584110</v>
       </c>
       <c r="R6" t="n">
-        <v>6401446</v>
+        <v>6401356</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,60 +1208,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129737526</v>
+        <v>129737898</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>58106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 56370, Mörghult, Sm</t>
+          <t>A56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584110</v>
+        <v>584009</v>
       </c>
       <c r="R7" t="n">
-        <v>6401356</v>
+        <v>6401446</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>129737728</v>
       </c>
       <c r="B8" t="n">
-        <v>105844</v>
+        <v>105846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>129737570</v>
       </c>
       <c r="B9" t="n">
-        <v>105844</v>
+        <v>105846</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>129737706</v>
       </c>
       <c r="B11" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>129737556</v>
       </c>
       <c r="B12" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>129737591</v>
       </c>
       <c r="B13" t="n">
-        <v>91581</v>
+        <v>91583</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1958,6 +1958,671 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129909748</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98785</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 56370, Mörghult, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>584042</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6401325</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129907685</v>
+      </c>
+      <c r="B15" t="n">
+        <v>105851</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ängnässjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>583951</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6401409</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129909807</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 56370, Mörghult, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>584042</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6401325</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129909753</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92881</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 56370, Mörghult, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>584009</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6401334</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129909724</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92252</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 56370, Mörghult, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>584039</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6401314</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129909738</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92881</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 56370, Mörghult, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>584026</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6401334</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gamla</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2623,6 +2623,345 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129914673</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92384</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>366</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Artomyces pyxidatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 56370, Mörghult, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>583899</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6401453</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Grov gammal asplåga</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129917987</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98786</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 56370, Mörghult, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>583962</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6401382</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129918139</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 56370, Mörghult, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>583994</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6401451</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Födosöksspår efter hästmyror</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129737606</v>
       </c>
       <c r="B2" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129737623</v>
       </c>
       <c r="B3" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129737717</v>
       </c>
       <c r="B4" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129737855</v>
       </c>
       <c r="B5" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>129737728</v>
       </c>
       <c r="B8" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>129737570</v>
       </c>
       <c r="B9" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>129737706</v>
       </c>
       <c r="B11" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>129737556</v>
       </c>
       <c r="B12" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>129909748</v>
       </c>
       <c r="B14" t="n">
-        <v>98785</v>
+        <v>98790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>129907685</v>
       </c>
       <c r="B15" t="n">
-        <v>105851</v>
+        <v>105856</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,46 +2184,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129909807</v>
+        <v>129909753</v>
       </c>
       <c r="B16" t="n">
-        <v>57896</v>
+        <v>92881</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2231,13 +2230,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584042</v>
+        <v>584009</v>
       </c>
       <c r="R16" t="n">
-        <v>6401325</v>
+        <v>6401334</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2275,6 +2274,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2286,52 +2286,53 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129909753</v>
+        <v>129909807</v>
       </c>
       <c r="B17" t="n">
-        <v>92881</v>
+        <v>57896</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2339,13 +2340,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584009</v>
+        <v>584042</v>
       </c>
       <c r="R17" t="n">
-        <v>6401334</v>
+        <v>6401325</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2383,7 +2384,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2395,17 +2395,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129909724</v>
+        <v>129909738</v>
       </c>
       <c r="B18" t="n">
-        <v>92252</v>
+        <v>92881</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,26 +2413,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584039</v>
+        <v>584026</v>
       </c>
       <c r="R18" t="n">
-        <v>6401314</v>
+        <v>6401334</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,6 +2486,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gamla</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2504,17 +2509,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129909738</v>
+        <v>129909724</v>
       </c>
       <c r="B19" t="n">
-        <v>92881</v>
+        <v>92252</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,26 +2527,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2557,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584026</v>
+        <v>584039</v>
       </c>
       <c r="R19" t="n">
-        <v>6401334</v>
+        <v>6401314</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,11 +2600,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Gamla</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2742,7 +2742,7 @@
         <v>129917987</v>
       </c>
       <c r="B21" t="n">
-        <v>98786</v>
+        <v>98790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129737606</v>
       </c>
       <c r="B2" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129737623</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129737717</v>
       </c>
       <c r="B4" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129737855</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,60 +1099,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129737526</v>
+        <v>129737898</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>58108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 56370, Mörghult, Sm</t>
+          <t>A56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584110</v>
+        <v>584009</v>
       </c>
       <c r="R6" t="n">
-        <v>6401356</v>
+        <v>6401446</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,52 +1200,60 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129737898</v>
+        <v>129737526</v>
       </c>
       <c r="B7" t="n">
-        <v>58106</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A56370, Mörghult, Sm</t>
+          <t>A 56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584009</v>
+        <v>584110</v>
       </c>
       <c r="R7" t="n">
-        <v>6401446</v>
+        <v>6401356</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>129737728</v>
       </c>
       <c r="B8" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>129737570</v>
       </c>
       <c r="B9" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>129737757</v>
       </c>
       <c r="B10" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>129737706</v>
       </c>
       <c r="B11" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>129737556</v>
       </c>
       <c r="B12" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>129737591</v>
       </c>
       <c r="B13" t="n">
-        <v>91583</v>
+        <v>91586</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>129909748</v>
       </c>
       <c r="B14" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>129907685</v>
       </c>
       <c r="B15" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>129909753</v>
       </c>
       <c r="B16" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129909807</v>
       </c>
       <c r="B17" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>129909738</v>
       </c>
       <c r="B18" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>129909724</v>
       </c>
       <c r="B19" t="n">
-        <v>92252</v>
+        <v>92255</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>129914673</v>
       </c>
       <c r="B20" t="n">
-        <v>92384</v>
+        <v>92387</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>129917987</v>
       </c>
       <c r="B21" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2857,7 +2857,7 @@
         <v>129918139</v>
       </c>
       <c r="B22" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -1099,52 +1099,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129737898</v>
+        <v>129737526</v>
       </c>
       <c r="B6" t="n">
-        <v>58108</v>
+        <v>57895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A56370, Mörghult, Sm</t>
+          <t>A 56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584009</v>
+        <v>584110</v>
       </c>
       <c r="R6" t="n">
-        <v>6401446</v>
+        <v>6401356</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,60 +1208,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129737526</v>
+        <v>129737898</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>58108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 56370, Mörghult, Sm</t>
+          <t>A56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584110</v>
+        <v>584009</v>
       </c>
       <c r="R7" t="n">
-        <v>6401356</v>
+        <v>6401446</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129909738</v>
+        <v>129909724</v>
       </c>
       <c r="B18" t="n">
-        <v>92884</v>
+        <v>92255</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,26 +2413,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584026</v>
+        <v>584039</v>
       </c>
       <c r="R18" t="n">
-        <v>6401334</v>
+        <v>6401314</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,11 +2486,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gamla</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2509,17 +2504,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129909724</v>
+        <v>129909738</v>
       </c>
       <c r="B19" t="n">
-        <v>92255</v>
+        <v>92884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,26 +2522,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2562,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584039</v>
+        <v>584026</v>
       </c>
       <c r="R19" t="n">
-        <v>6401314</v>
+        <v>6401334</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2600,6 +2595,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gamla</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -2184,45 +2184,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129909753</v>
+        <v>129909807</v>
       </c>
       <c r="B16" t="n">
-        <v>92884</v>
+        <v>57895</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2230,13 +2231,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584009</v>
+        <v>584042</v>
       </c>
       <c r="R16" t="n">
-        <v>6401334</v>
+        <v>6401325</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2274,7 +2275,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2286,53 +2286,52 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129909807</v>
+        <v>129909753</v>
       </c>
       <c r="B17" t="n">
-        <v>57895</v>
+        <v>92884</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2340,13 +2339,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584042</v>
+        <v>584009</v>
       </c>
       <c r="R17" t="n">
-        <v>6401325</v>
+        <v>6401334</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2384,6 +2383,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129737606</v>
       </c>
       <c r="B2" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129737623</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129737717</v>
       </c>
       <c r="B4" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129737855</v>
       </c>
       <c r="B5" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129737526</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>129737898</v>
       </c>
       <c r="B7" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>129737728</v>
       </c>
       <c r="B8" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>129737570</v>
       </c>
       <c r="B9" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>129737757</v>
       </c>
       <c r="B10" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>129737706</v>
       </c>
       <c r="B11" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>129737556</v>
       </c>
       <c r="B12" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>129737591</v>
       </c>
       <c r="B13" t="n">
-        <v>91586</v>
+        <v>91589</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>129909748</v>
       </c>
       <c r="B14" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>129907685</v>
       </c>
       <c r="B15" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,46 +2184,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129909807</v>
+        <v>129909753</v>
       </c>
       <c r="B16" t="n">
-        <v>57895</v>
+        <v>92887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2231,13 +2230,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584042</v>
+        <v>584009</v>
       </c>
       <c r="R16" t="n">
-        <v>6401325</v>
+        <v>6401334</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2275,6 +2274,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2286,52 +2286,53 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129909753</v>
+        <v>129909807</v>
       </c>
       <c r="B17" t="n">
-        <v>92884</v>
+        <v>57898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2339,13 +2340,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584009</v>
+        <v>584042</v>
       </c>
       <c r="R17" t="n">
-        <v>6401334</v>
+        <v>6401325</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2383,7 +2384,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2395,17 +2395,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129909724</v>
+        <v>129909738</v>
       </c>
       <c r="B18" t="n">
-        <v>92255</v>
+        <v>92887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,26 +2413,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584039</v>
+        <v>584026</v>
       </c>
       <c r="R18" t="n">
-        <v>6401314</v>
+        <v>6401334</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,6 +2486,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gamla</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2504,17 +2509,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129909738</v>
+        <v>129909724</v>
       </c>
       <c r="B19" t="n">
-        <v>92884</v>
+        <v>92258</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,26 +2527,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2557,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584026</v>
+        <v>584039</v>
       </c>
       <c r="R19" t="n">
-        <v>6401334</v>
+        <v>6401314</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,11 +2600,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Gamla</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2628,7 +2628,7 @@
         <v>129914673</v>
       </c>
       <c r="B20" t="n">
-        <v>92387</v>
+        <v>92390</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>129917987</v>
       </c>
       <c r="B21" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>129918139</v>
       </c>
       <c r="B22" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -2184,45 +2184,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129909753</v>
+        <v>129909807</v>
       </c>
       <c r="B16" t="n">
-        <v>92887</v>
+        <v>57898</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2230,13 +2231,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584009</v>
+        <v>584042</v>
       </c>
       <c r="R16" t="n">
-        <v>6401334</v>
+        <v>6401325</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2274,7 +2275,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2286,53 +2286,52 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129909807</v>
+        <v>129909753</v>
       </c>
       <c r="B17" t="n">
-        <v>57898</v>
+        <v>92887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2340,13 +2339,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584042</v>
+        <v>584009</v>
       </c>
       <c r="R17" t="n">
-        <v>6401325</v>
+        <v>6401334</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2384,6 +2383,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129737606</v>
       </c>
       <c r="B2" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129737623</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129737717</v>
       </c>
       <c r="B4" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129737855</v>
       </c>
       <c r="B5" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,60 +1099,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129737526</v>
+        <v>129737898</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>58111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 56370, Mörghult, Sm</t>
+          <t>A56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584110</v>
+        <v>584009</v>
       </c>
       <c r="R6" t="n">
-        <v>6401356</v>
+        <v>6401446</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,52 +1200,60 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129737898</v>
+        <v>129737526</v>
       </c>
       <c r="B7" t="n">
-        <v>58111</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A56370, Mörghult, Sm</t>
+          <t>A 56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584009</v>
+        <v>584110</v>
       </c>
       <c r="R7" t="n">
-        <v>6401446</v>
+        <v>6401356</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>129737728</v>
       </c>
       <c r="B8" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>129737570</v>
       </c>
       <c r="B9" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>129737706</v>
       </c>
       <c r="B11" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>129737556</v>
       </c>
       <c r="B12" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>129737591</v>
       </c>
       <c r="B13" t="n">
-        <v>91589</v>
+        <v>91590</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>129909748</v>
       </c>
       <c r="B14" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>129907685</v>
       </c>
       <c r="B15" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,46 +2184,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129909807</v>
+        <v>129909753</v>
       </c>
       <c r="B16" t="n">
-        <v>57898</v>
+        <v>92888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2231,13 +2230,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584042</v>
+        <v>584009</v>
       </c>
       <c r="R16" t="n">
-        <v>6401325</v>
+        <v>6401334</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2275,6 +2274,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2286,52 +2286,53 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129909753</v>
+        <v>129909807</v>
       </c>
       <c r="B17" t="n">
-        <v>92887</v>
+        <v>57898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2339,13 +2340,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584009</v>
+        <v>584042</v>
       </c>
       <c r="R17" t="n">
-        <v>6401334</v>
+        <v>6401325</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2383,7 +2384,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2395,17 +2395,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129909738</v>
+        <v>129909724</v>
       </c>
       <c r="B18" t="n">
-        <v>92887</v>
+        <v>92259</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,26 +2413,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584026</v>
+        <v>584039</v>
       </c>
       <c r="R18" t="n">
-        <v>6401334</v>
+        <v>6401314</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,11 +2486,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gamla</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2509,17 +2504,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129909724</v>
+        <v>129909738</v>
       </c>
       <c r="B19" t="n">
-        <v>92258</v>
+        <v>92888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,26 +2522,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2562,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584039</v>
+        <v>584026</v>
       </c>
       <c r="R19" t="n">
-        <v>6401314</v>
+        <v>6401334</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2600,6 +2595,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gamla</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2628,7 +2628,7 @@
         <v>129914673</v>
       </c>
       <c r="B20" t="n">
-        <v>92390</v>
+        <v>92391</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>129917987</v>
       </c>
       <c r="B21" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129737606</v>
       </c>
       <c r="B2" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129737623</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129737717</v>
       </c>
       <c r="B4" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129737855</v>
       </c>
       <c r="B5" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129737898</v>
       </c>
       <c r="B6" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>129737526</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>129737728</v>
       </c>
       <c r="B8" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>129737570</v>
       </c>
       <c r="B9" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>129737757</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>129737706</v>
       </c>
       <c r="B11" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>129737556</v>
       </c>
       <c r="B12" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>129737591</v>
       </c>
       <c r="B13" t="n">
-        <v>91590</v>
+        <v>91607</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>129909748</v>
       </c>
       <c r="B14" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>129907685</v>
       </c>
       <c r="B15" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>129909753</v>
       </c>
       <c r="B16" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129909807</v>
       </c>
       <c r="B17" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>129909724</v>
       </c>
       <c r="B18" t="n">
-        <v>92259</v>
+        <v>92276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>129909738</v>
       </c>
       <c r="B19" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>129914673</v>
       </c>
       <c r="B20" t="n">
-        <v>92391</v>
+        <v>92408</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>129917987</v>
       </c>
       <c r="B21" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129909738</v>
+        <v>129909724</v>
       </c>
       <c r="B18" t="n">
-        <v>92921</v>
+        <v>92292</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,26 +2413,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584026</v>
+        <v>584039</v>
       </c>
       <c r="R18" t="n">
-        <v>6401334</v>
+        <v>6401314</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,11 +2486,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gamla</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2509,17 +2504,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129909724</v>
+        <v>129909738</v>
       </c>
       <c r="B19" t="n">
-        <v>92292</v>
+        <v>92921</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,26 +2522,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2562,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584039</v>
+        <v>584026</v>
       </c>
       <c r="R19" t="n">
-        <v>6401314</v>
+        <v>6401334</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2600,6 +2595,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gamla</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -2184,45 +2184,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129909753</v>
+        <v>129909807</v>
       </c>
       <c r="B16" t="n">
-        <v>92921</v>
+        <v>57900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2230,13 +2231,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584009</v>
+        <v>584042</v>
       </c>
       <c r="R16" t="n">
-        <v>6401334</v>
+        <v>6401325</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2274,7 +2275,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2286,53 +2286,52 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129909807</v>
+        <v>129909753</v>
       </c>
       <c r="B17" t="n">
-        <v>57900</v>
+        <v>92921</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2340,13 +2339,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584042</v>
+        <v>584009</v>
       </c>
       <c r="R17" t="n">
-        <v>6401325</v>
+        <v>6401334</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2384,6 +2383,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2395,17 +2395,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129909724</v>
+        <v>129909738</v>
       </c>
       <c r="B18" t="n">
-        <v>92292</v>
+        <v>92921</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,26 +2413,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584039</v>
+        <v>584026</v>
       </c>
       <c r="R18" t="n">
-        <v>6401314</v>
+        <v>6401334</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,6 +2486,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gamla</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2504,17 +2509,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129909738</v>
+        <v>129909724</v>
       </c>
       <c r="B19" t="n">
-        <v>92921</v>
+        <v>92292</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,26 +2527,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2557,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584026</v>
+        <v>584039</v>
       </c>
       <c r="R19" t="n">
-        <v>6401334</v>
+        <v>6401314</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,11 +2600,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Gamla</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -1963,7 +1963,7 @@
         <v>129909748</v>
       </c>
       <c r="B14" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>129907685</v>
       </c>
       <c r="B15" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,46 +2184,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129909807</v>
+        <v>129909753</v>
       </c>
       <c r="B16" t="n">
-        <v>57900</v>
+        <v>92923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2231,13 +2230,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584042</v>
+        <v>584009</v>
       </c>
       <c r="R16" t="n">
-        <v>6401325</v>
+        <v>6401334</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2275,6 +2274,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2286,52 +2286,53 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129909753</v>
+        <v>129909807</v>
       </c>
       <c r="B17" t="n">
-        <v>92921</v>
+        <v>57900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2339,13 +2340,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584009</v>
+        <v>584042</v>
       </c>
       <c r="R17" t="n">
-        <v>6401334</v>
+        <v>6401325</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2383,7 +2384,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2395,17 +2395,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129909738</v>
+        <v>129909724</v>
       </c>
       <c r="B18" t="n">
-        <v>92921</v>
+        <v>92294</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,26 +2413,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584026</v>
+        <v>584039</v>
       </c>
       <c r="R18" t="n">
-        <v>6401334</v>
+        <v>6401314</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,11 +2486,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gamla</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2509,17 +2504,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129909724</v>
+        <v>129909738</v>
       </c>
       <c r="B19" t="n">
-        <v>92292</v>
+        <v>92923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,26 +2522,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2562,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584039</v>
+        <v>584026</v>
       </c>
       <c r="R19" t="n">
-        <v>6401314</v>
+        <v>6401334</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2600,6 +2595,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gamla</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2628,7 +2628,7 @@
         <v>129914673</v>
       </c>
       <c r="B20" t="n">
-        <v>92424</v>
+        <v>92426</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>129917987</v>
       </c>
       <c r="B21" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -1963,7 +1963,7 @@
         <v>129909748</v>
       </c>
       <c r="B14" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>129907685</v>
       </c>
       <c r="B15" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,45 +2184,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129909753</v>
+        <v>129909807</v>
       </c>
       <c r="B16" t="n">
-        <v>92923</v>
+        <v>57985</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2230,13 +2231,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584009</v>
+        <v>584042</v>
       </c>
       <c r="R16" t="n">
-        <v>6401334</v>
+        <v>6401325</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2274,7 +2275,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2286,53 +2286,52 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129909807</v>
+        <v>129909753</v>
       </c>
       <c r="B17" t="n">
-        <v>57900</v>
+        <v>93010</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2340,13 +2339,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584042</v>
+        <v>584009</v>
       </c>
       <c r="R17" t="n">
-        <v>6401325</v>
+        <v>6401334</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2384,6 +2383,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2395,17 +2395,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129909724</v>
+        <v>129909738</v>
       </c>
       <c r="B18" t="n">
-        <v>92294</v>
+        <v>93010</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,26 +2413,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584039</v>
+        <v>584026</v>
       </c>
       <c r="R18" t="n">
-        <v>6401314</v>
+        <v>6401334</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,6 +2486,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gamla</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2504,17 +2509,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129909738</v>
+        <v>129909724</v>
       </c>
       <c r="B19" t="n">
-        <v>92923</v>
+        <v>92381</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,26 +2527,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2557,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584026</v>
+        <v>584039</v>
       </c>
       <c r="R19" t="n">
-        <v>6401334</v>
+        <v>6401314</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,11 +2600,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Gamla</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2628,7 +2628,7 @@
         <v>129914673</v>
       </c>
       <c r="B20" t="n">
-        <v>92426</v>
+        <v>92513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>129917987</v>
       </c>
       <c r="B21" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>129918139</v>
       </c>
       <c r="B22" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -1963,7 +1963,7 @@
         <v>129909748</v>
       </c>
       <c r="B14" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>129907685</v>
       </c>
       <c r="B15" t="n">
-        <v>105987</v>
+        <v>105900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,46 +2184,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129909807</v>
+        <v>129909753</v>
       </c>
       <c r="B16" t="n">
-        <v>57985</v>
+        <v>92923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2231,13 +2230,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584042</v>
+        <v>584009</v>
       </c>
       <c r="R16" t="n">
-        <v>6401325</v>
+        <v>6401334</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2275,6 +2274,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2286,52 +2286,53 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129909753</v>
+        <v>129909807</v>
       </c>
       <c r="B17" t="n">
-        <v>93010</v>
+        <v>57900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2339,13 +2340,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584009</v>
+        <v>584042</v>
       </c>
       <c r="R17" t="n">
-        <v>6401334</v>
+        <v>6401325</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2383,7 +2384,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2395,17 +2395,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129909738</v>
+        <v>129909724</v>
       </c>
       <c r="B18" t="n">
-        <v>93010</v>
+        <v>92294</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,26 +2413,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584026</v>
+        <v>584039</v>
       </c>
       <c r="R18" t="n">
-        <v>6401334</v>
+        <v>6401314</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,11 +2486,6 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gamla</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2509,17 +2504,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129909724</v>
+        <v>129909738</v>
       </c>
       <c r="B19" t="n">
-        <v>92381</v>
+        <v>92923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,26 +2522,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2562,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584039</v>
+        <v>584026</v>
       </c>
       <c r="R19" t="n">
-        <v>6401314</v>
+        <v>6401334</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2600,6 +2595,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gamla</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2628,7 +2628,7 @@
         <v>129914673</v>
       </c>
       <c r="B20" t="n">
-        <v>92513</v>
+        <v>92426</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>129917987</v>
       </c>
       <c r="B21" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>129918139</v>
       </c>
       <c r="B22" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 56370-2025 artfynd.xlsx
+++ b/artfynd/A 56370-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129737606</v>
+        <v>129914673</v>
       </c>
       <c r="B2" t="n">
-        <v>105896</v>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583947</v>
+        <v>583899</v>
       </c>
       <c r="R2" t="n">
-        <v>6401540</v>
+        <v>6401453</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Grov gammal asplåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,49 +782,52 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129737623</v>
+        <v>129909738</v>
       </c>
       <c r="B3" t="n">
-        <v>98830</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583967</v>
+        <v>584026</v>
       </c>
       <c r="R3" t="n">
-        <v>6401506</v>
+        <v>6401334</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,12 +865,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gamla</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,49 +896,52 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129737717</v>
+        <v>129909753</v>
       </c>
       <c r="B4" t="n">
-        <v>105896</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583950</v>
+        <v>584009</v>
       </c>
       <c r="R4" t="n">
-        <v>6401492</v>
+        <v>6401334</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,12 +979,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,49 +1005,52 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129737855</v>
+        <v>129737591</v>
       </c>
       <c r="B5" t="n">
-        <v>98830</v>
+        <v>91893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1036,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584069</v>
+        <v>583974</v>
       </c>
       <c r="R5" t="n">
-        <v>6401364</v>
+        <v>6401513</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1094,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På högstubbe av asp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,46 +1126,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129737526</v>
+        <v>129909724</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>92567</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1146,13 +1172,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584110</v>
+        <v>584039</v>
       </c>
       <c r="R6" t="n">
-        <v>6401356</v>
+        <v>6401314</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,12 +1202,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,6 +1216,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1208,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129737898</v>
+        <v>129918139</v>
       </c>
       <c r="B7" t="n">
-        <v>58112</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,16 +1246,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1239,21 +1266,25 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A56370, Mörghult, Sm</t>
+          <t>A 56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584009</v>
+        <v>583994</v>
       </c>
       <c r="R7" t="n">
-        <v>6401446</v>
+        <v>6401451</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1277,12 +1308,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födosöksspår efter hästmyror</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,49 +1338,53 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129737728</v>
+        <v>129737526</v>
       </c>
       <c r="B8" t="n">
-        <v>105896</v>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1352,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583950</v>
+        <v>584110</v>
       </c>
       <c r="R8" t="n">
-        <v>6401493</v>
+        <v>6401356</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1396,7 +1436,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1415,42 +1454,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129737570</v>
+        <v>129737757</v>
       </c>
       <c r="B9" t="n">
-        <v>105896</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1458,13 +1501,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583988</v>
+        <v>583899</v>
       </c>
       <c r="R9" t="n">
-        <v>6401517</v>
+        <v>6401532</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1502,7 +1545,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1521,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129737757</v>
+        <v>129909807</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,10 +1610,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583899</v>
+        <v>584042</v>
       </c>
       <c r="R10" t="n">
-        <v>6401532</v>
+        <v>6401325</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1598,12 +1640,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1630,35 +1672,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129737706</v>
+        <v>129907658</v>
       </c>
       <c r="B11" t="n">
-        <v>98830</v>
+        <v>111175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1669,17 +1715,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 56370, Mörghult, Sm</t>
+          <t>Ängnässjön, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583986</v>
+        <v>584161</v>
       </c>
       <c r="R11" t="n">
-        <v>6401495</v>
+        <v>6401327</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1703,12 +1749,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växer på en ek.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,12 +1775,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1739,7 +1790,7 @@
         <v>129737556</v>
       </c>
       <c r="B12" t="n">
-        <v>98830</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,45 +1897,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129737591</v>
+        <v>129737623</v>
       </c>
       <c r="B13" t="n">
-        <v>91623</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1892,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583974</v>
+        <v>583967</v>
       </c>
       <c r="R13" t="n">
-        <v>6401513</v>
+        <v>6401506</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,11 +1976,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På högstubbe av asp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1960,10 +2003,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129909748</v>
+        <v>129737695</v>
       </c>
       <c r="B14" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,16 +2031,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2007,10 +2042,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584042</v>
+        <v>583967</v>
       </c>
       <c r="R14" t="n">
-        <v>6401325</v>
+        <v>6401552</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2037,12 +2072,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,71 +2098,63 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129907685</v>
+        <v>129737706</v>
       </c>
       <c r="B15" t="n">
-        <v>105987</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ängnässjön, Sm</t>
+          <t>A 56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583951</v>
+        <v>583986</v>
       </c>
       <c r="R15" t="n">
-        <v>6401409</v>
+        <v>6401495</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2151,12 +2178,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2172,57 +2199,54 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129909753</v>
+        <v>129737855</v>
       </c>
       <c r="B16" t="n">
-        <v>93010</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2230,10 +2254,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584009</v>
+        <v>584069</v>
       </c>
       <c r="R16" t="n">
-        <v>6401334</v>
+        <v>6401364</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,12 +2284,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,53 +2310,53 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129909807</v>
+        <v>129909748</v>
       </c>
       <c r="B17" t="n">
-        <v>57985</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2384,6 +2408,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2395,52 +2420,53 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129909724</v>
+        <v>129917987</v>
       </c>
       <c r="B18" t="n">
-        <v>92381</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2448,10 +2474,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584039</v>
+        <v>583962</v>
       </c>
       <c r="R18" t="n">
-        <v>6401314</v>
+        <v>6401382</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2478,12 +2504,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,17 +2535,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129909738</v>
+        <v>129737570</v>
       </c>
       <c r="B19" t="n">
-        <v>93010</v>
+        <v>106243</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,34 +2553,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2557,10 +2585,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584026</v>
+        <v>583988</v>
       </c>
       <c r="R19" t="n">
-        <v>6401334</v>
+        <v>6401517</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2587,17 +2615,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Gamla</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2618,52 +2641,49 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129914673</v>
+        <v>129737606</v>
       </c>
       <c r="B20" t="n">
-        <v>92513</v>
+        <v>106243</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>366</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2671,10 +2691,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583899</v>
+        <v>583947</v>
       </c>
       <c r="R20" t="n">
-        <v>6401453</v>
+        <v>6401540</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2701,17 +2721,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Grov gammal asplåga</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2732,46 +2747,42 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129917987</v>
+        <v>129737717</v>
       </c>
       <c r="B21" t="n">
-        <v>98920</v>
+        <v>106243</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2786,10 +2797,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583962</v>
+        <v>583950</v>
       </c>
       <c r="R21" t="n">
-        <v>6401382</v>
+        <v>6401492</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2816,17 +2827,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2847,49 +2853,49 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129918139</v>
+        <v>129737728</v>
       </c>
       <c r="B22" t="n">
-        <v>57823</v>
+        <v>106243</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2897,10 +2903,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583994</v>
+        <v>583950</v>
       </c>
       <c r="R22" t="n">
-        <v>6401451</v>
+        <v>6401493</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2927,17 +2933,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Födosöksspår efter hästmyror</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2946,6 +2947,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2957,10 +2959,124 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129907685</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ängnässjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>583951</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6401409</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
